--- a/StructureDefinition-lmdi-condition.xlsx
+++ b/StructureDefinition-lmdi-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.7</t>
+    <t>1.0.8</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-condition.xlsx
+++ b/StructureDefinition-lmdi-condition.xlsx
@@ -9525,7 +9525,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>91</v>

--- a/StructureDefinition-lmdi-condition.xlsx
+++ b/StructureDefinition-lmdi-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-condition.xlsx
+++ b/StructureDefinition-lmdi-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-condition.xlsx
+++ b/StructureDefinition-lmdi-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.1.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-condition.xlsx
+++ b/StructureDefinition-lmdi-condition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
